--- a/calibration mixes.xlsx
+++ b/calibration mixes.xlsx
@@ -1017,14 +1017,14 @@
       <c r="E21" s="5"/>
       <c r="F21" s="4"/>
       <c r="G21" s="4">
-        <f>C21/D21</f>
+        <f t="shared" ref="G21:G29" si="7">C21/D21</f>
         <v>220</v>
       </c>
       <c r="H21" s="4">
         <v>1.0840000000000001</v>
       </c>
       <c r="I21" s="6">
-        <f>10*H21*(143.254*H21^3-648.67*H21^2+1125.805*H21-620.389)-G21</f>
+        <f t="shared" ref="I21:I29" si="8">10*H21*(143.254*H21^3-648.67*H21^2+1125.805*H21-620.389)-G21</f>
         <v>-0.69205358035341646</v>
       </c>
       <c r="J21" s="4"/>
@@ -1038,26 +1038,26 @@
         <v>-0.7</v>
       </c>
       <c r="C22" s="9">
-        <f>E22*C21/D21</f>
+        <f t="shared" ref="C22:C29" si="9">E22*C21/D21</f>
         <v>396</v>
       </c>
       <c r="D22" s="9">
         <v>2.5</v>
       </c>
       <c r="E22" s="10">
-        <f>2.5+B22</f>
+        <f t="shared" ref="E22:E29" si="10">2.5+B22</f>
         <v>1.8</v>
       </c>
       <c r="F22" s="9"/>
       <c r="G22" s="9">
-        <f>C22/D22</f>
+        <f t="shared" si="7"/>
         <v>158.4</v>
       </c>
       <c r="H22" s="9">
         <v>1.0609999999999999</v>
       </c>
       <c r="I22" s="18">
-        <f>10*H22*(143.254*H22^3-648.67*H22^2+1125.805*H22-620.389)-G22</f>
+        <f t="shared" si="8"/>
         <v>0.42964450532502951</v>
       </c>
       <c r="J22" s="9"/>
@@ -1074,31 +1074,31 @@
         <v>-0.7</v>
       </c>
       <c r="C23" s="9">
-        <f>E23*C22/D22</f>
+        <f t="shared" si="9"/>
         <v>285.12</v>
       </c>
       <c r="D23" s="9">
         <v>2.5</v>
       </c>
       <c r="E23" s="10">
-        <f>2.5+B23</f>
+        <f t="shared" si="10"/>
         <v>1.8</v>
       </c>
       <c r="F23" s="9"/>
       <c r="G23" s="9">
-        <f>C23/D23</f>
+        <f t="shared" si="7"/>
         <v>114.048</v>
       </c>
       <c r="H23" s="9">
         <v>1.044</v>
       </c>
       <c r="I23" s="11">
-        <f>10*H23*(143.254*H23^3-648.67*H23^2+1125.805*H23-620.389)-G23</f>
+        <f t="shared" si="8"/>
         <v>0.27402003408663234</v>
       </c>
       <c r="J23" s="9"/>
       <c r="K23" s="12">
-        <f t="shared" ref="K23:K25" si="7">H22-H23</f>
+        <f t="shared" ref="K23:K25" si="11">H22-H23</f>
         <v>1.6999999999999904E-2</v>
       </c>
     </row>
@@ -1110,31 +1110,31 @@
         <v>-0.8</v>
       </c>
       <c r="C24" s="9">
-        <f>E24*C23/D23</f>
+        <f t="shared" si="9"/>
         <v>193.88159999999999</v>
       </c>
       <c r="D24" s="9">
         <v>2.5</v>
       </c>
       <c r="E24" s="10">
-        <f>2.5+B24</f>
+        <f t="shared" si="10"/>
         <v>1.7</v>
       </c>
       <c r="F24" s="9"/>
       <c r="G24" s="9">
-        <f>C24/D24</f>
+        <f t="shared" si="7"/>
         <v>77.552639999999997</v>
       </c>
       <c r="H24" s="9">
         <v>1.03</v>
       </c>
       <c r="I24" s="11">
-        <f>10*H24*(143.254*H24^3-648.67*H24^2+1125.805*H24-620.389)-G24</f>
+        <f t="shared" si="8"/>
         <v>0.25006477740014077</v>
       </c>
       <c r="J24" s="9"/>
       <c r="K24" s="12">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>1.4000000000000012E-2</v>
       </c>
     </row>
@@ -1146,31 +1146,31 @@
         <v>-0.9</v>
       </c>
       <c r="C25" s="9">
-        <f>E25*C24/D24</f>
+        <f t="shared" si="9"/>
         <v>124.08422399999999</v>
       </c>
       <c r="D25" s="9">
         <v>2.5</v>
       </c>
       <c r="E25" s="10">
-        <f>2.5+B25</f>
+        <f t="shared" si="10"/>
         <v>1.6</v>
       </c>
       <c r="F25" s="9"/>
       <c r="G25" s="9">
-        <f>C25/D25</f>
+        <f t="shared" si="7"/>
         <v>49.633689599999997</v>
       </c>
       <c r="H25" s="9">
         <v>1.0189999999999999</v>
       </c>
       <c r="I25" s="18">
-        <f>10*H25*(143.254*H25^3-648.67*H25^2+1125.805*H25-620.389)-G25</f>
+        <f t="shared" si="8"/>
         <v>-0.43362042781448906</v>
       </c>
       <c r="J25" s="9"/>
       <c r="K25" s="12">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>1.1000000000000121E-2</v>
       </c>
     </row>
@@ -1182,31 +1182,31 @@
         <v>-0.8</v>
       </c>
       <c r="C26" s="9">
-        <f>E26*C25/D25</f>
+        <f t="shared" si="9"/>
         <v>84.377272320000003</v>
       </c>
       <c r="D26" s="9">
         <v>2.5</v>
       </c>
       <c r="E26" s="10">
-        <f>2.5+B26</f>
+        <f t="shared" si="10"/>
         <v>1.7</v>
       </c>
       <c r="F26" s="9"/>
       <c r="G26" s="9">
-        <f>C26/D26</f>
+        <f t="shared" si="7"/>
         <v>33.750908928000001</v>
       </c>
       <c r="H26" s="9">
         <v>1.0129999999999999</v>
       </c>
       <c r="I26" s="11">
-        <f>10*H26*(143.254*H26^3-648.67*H26^2+1125.805*H26-620.389)-G26</f>
+        <f t="shared" si="8"/>
         <v>-0.11657102160572919</v>
       </c>
       <c r="J26" s="9"/>
       <c r="K26" s="12">
-        <f t="shared" ref="K26" si="8">H25-H26</f>
+        <f t="shared" ref="K26" si="12">H25-H26</f>
         <v>6.0000000000000053E-3</v>
       </c>
     </row>
@@ -1218,31 +1218,31 @@
         <v>-1</v>
       </c>
       <c r="C27" s="9">
-        <f>E27*C26/D26</f>
+        <f t="shared" si="9"/>
         <v>50.626363392000002</v>
       </c>
       <c r="D27" s="9">
         <v>2.5</v>
       </c>
       <c r="E27" s="10">
-        <f>2.5+B27</f>
+        <f t="shared" si="10"/>
         <v>1.5</v>
       </c>
       <c r="F27" s="9"/>
       <c r="G27" s="9">
-        <f>C27/D27</f>
+        <f t="shared" si="7"/>
         <v>20.2505453568</v>
       </c>
       <c r="H27" s="9">
         <v>1.008</v>
       </c>
       <c r="I27" s="18">
-        <f>10*H27*(143.254*H27^3-648.67*H27^2+1125.805*H27-620.389)-G27</f>
+        <f t="shared" si="8"/>
         <v>0.43239732240600759</v>
       </c>
       <c r="J27" s="9"/>
       <c r="K27" s="12">
-        <f t="shared" ref="K27" si="9">H26-H27</f>
+        <f t="shared" ref="K27" si="13">H26-H27</f>
         <v>4.9999999999998934E-3</v>
       </c>
     </row>
@@ -1254,31 +1254,31 @@
         <v>-1.2</v>
       </c>
       <c r="C28" s="9">
-        <f>E28*C27/D27</f>
+        <f t="shared" si="9"/>
         <v>26.325708963840004</v>
       </c>
       <c r="D28" s="9">
         <v>2.5</v>
       </c>
       <c r="E28" s="10">
-        <f>2.5+B28</f>
+        <f t="shared" si="10"/>
         <v>1.3</v>
       </c>
       <c r="F28" s="9"/>
       <c r="G28" s="9">
-        <f>C28/D28</f>
+        <f t="shared" si="7"/>
         <v>10.530283585536001</v>
       </c>
       <c r="H28" s="9">
         <v>1.004</v>
       </c>
       <c r="I28" s="11">
-        <f>10*H28*(143.254*H28^3-648.67*H28^2+1125.805*H28-620.389)-G28</f>
+        <f t="shared" si="8"/>
         <v>-0.1949605973652595</v>
       </c>
       <c r="J28" s="9"/>
       <c r="K28" s="12">
-        <f t="shared" ref="K28" si="10">H27-H28</f>
+        <f t="shared" ref="K28" si="14">H27-H28</f>
         <v>4.0000000000000036E-3</v>
       </c>
     </row>
@@ -1290,31 +1290,31 @@
         <v>-2.5</v>
       </c>
       <c r="C29" s="14">
-        <f>E29*C28/D28</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="D29" s="14">
         <v>2.5</v>
       </c>
       <c r="E29" s="15">
-        <f>2.5+B29</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="F29" s="14"/>
       <c r="G29" s="14">
-        <f>C29/D29</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="H29" s="14">
         <v>1</v>
       </c>
       <c r="I29" s="16">
-        <f>10*H29*(143.254*H29^3-648.67*H29^2+1125.805*H29-620.389)-G29</f>
+        <f t="shared" si="8"/>
         <v>1.1368683772161603E-12</v>
       </c>
       <c r="J29" s="14"/>
       <c r="K29" s="17">
-        <f t="shared" ref="K29" si="11">H28-H29</f>
+        <f t="shared" ref="K29" si="15">H28-H29</f>
         <v>4.0000000000000036E-3</v>
       </c>
     </row>
@@ -1351,14 +1351,14 @@
       <c r="E33" s="5"/>
       <c r="F33" s="4"/>
       <c r="G33" s="4">
-        <f>C33/D33</f>
+        <f t="shared" ref="G33:G40" si="16">C33/D33</f>
         <v>212</v>
       </c>
       <c r="H33" s="4">
         <v>1.081</v>
       </c>
       <c r="I33" s="6">
-        <f>10*H33*(143.254*H33^3-648.67*H33^2+1125.805*H33-620.389)-G33</f>
+        <f t="shared" ref="I33:I40" si="17">10*H33*(143.254*H33^3-648.67*H33^2+1125.805*H33-620.389)-G33</f>
         <v>-0.5968006344400294</v>
       </c>
       <c r="J33" s="4"/>
@@ -1372,26 +1372,26 @@
         <v>-0.6</v>
       </c>
       <c r="C34" s="9">
-        <f>E34*C33/D33</f>
+        <f t="shared" ref="C34:C40" si="18">E34*C33/D33</f>
         <v>402.8</v>
       </c>
       <c r="D34" s="9">
         <v>2.5</v>
       </c>
       <c r="E34" s="10">
-        <f>2.5+B34</f>
+        <f t="shared" ref="E34:E40" si="19">2.5+B34</f>
         <v>1.9</v>
       </c>
       <c r="F34" s="9"/>
       <c r="G34" s="9">
-        <f>C34/D34</f>
+        <f t="shared" si="16"/>
         <v>161.12</v>
       </c>
       <c r="H34" s="9">
         <v>1.0620000000000001</v>
       </c>
       <c r="I34" s="11">
-        <f>10*H34*(143.254*H34^3-648.67*H34^2+1125.805*H34-620.389)-G34</f>
+        <f t="shared" si="17"/>
         <v>0.33302538725251907</v>
       </c>
       <c r="J34" s="9"/>
@@ -1408,31 +1408,31 @@
         <v>-0.8</v>
       </c>
       <c r="C35" s="9">
-        <f>E35*C34/D34</f>
+        <f t="shared" si="18"/>
         <v>273.904</v>
       </c>
       <c r="D35" s="9">
         <v>2.5</v>
       </c>
       <c r="E35" s="10">
-        <f>2.5+B35</f>
+        <f t="shared" si="19"/>
         <v>1.7</v>
       </c>
       <c r="F35" s="9"/>
       <c r="G35" s="9">
-        <f>C35/D35</f>
+        <f t="shared" si="16"/>
         <v>109.5616</v>
       </c>
       <c r="H35" s="9">
         <v>1.042</v>
       </c>
       <c r="I35" s="18">
-        <f>10*H35*(143.254*H35^3-648.67*H35^2+1125.805*H35-620.389)-G35</f>
+        <f t="shared" si="17"/>
         <v>-0.46426574652980435</v>
       </c>
       <c r="J35" s="9"/>
       <c r="K35" s="12">
-        <f t="shared" ref="K35:K37" si="12">H34-H35</f>
+        <f t="shared" ref="K35:K37" si="20">H34-H35</f>
         <v>2.0000000000000018E-2</v>
       </c>
     </row>
@@ -1444,31 +1444,31 @@
         <v>-0.9</v>
       </c>
       <c r="C36" s="9">
-        <f>E36*C35/D35</f>
+        <f t="shared" si="18"/>
         <v>175.29856000000001</v>
       </c>
       <c r="D36" s="9">
         <v>2.5</v>
       </c>
       <c r="E36" s="10">
-        <f>2.5+B36</f>
+        <f t="shared" si="19"/>
         <v>1.6</v>
       </c>
       <c r="F36" s="9"/>
       <c r="G36" s="9">
-        <f>C36/D36</f>
+        <f t="shared" si="16"/>
         <v>70.119424000000009</v>
       </c>
       <c r="H36" s="9">
         <v>1.0269999999999999</v>
       </c>
       <c r="I36" s="11">
-        <f>10*H36*(143.254*H36^3-648.67*H36^2+1125.805*H36-620.389)-G36</f>
+        <f t="shared" si="17"/>
         <v>-0.12562815632962554</v>
       </c>
       <c r="J36" s="9"/>
       <c r="K36" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="20"/>
         <v>1.5000000000000124E-2</v>
       </c>
     </row>
@@ -1480,31 +1480,31 @@
         <v>-1.1000000000000001</v>
       </c>
       <c r="C37" s="9">
-        <f>E37*C36/D36</f>
+        <f t="shared" si="18"/>
         <v>98.16719359999999</v>
       </c>
       <c r="D37" s="9">
         <v>2.5</v>
       </c>
       <c r="E37" s="10">
-        <f>2.5+B37</f>
+        <f t="shared" si="19"/>
         <v>1.4</v>
       </c>
       <c r="F37" s="9"/>
       <c r="G37" s="9">
-        <f>C37/D37</f>
+        <f t="shared" si="16"/>
         <v>39.266877439999995</v>
       </c>
       <c r="H37" s="9">
         <v>1.0149999999999999</v>
       </c>
       <c r="I37" s="18">
-        <f>10*H37*(143.254*H37^3-648.67*H37^2+1125.805*H37-620.389)-G37</f>
+        <f t="shared" si="17"/>
         <v>-0.44684049016068172</v>
       </c>
       <c r="J37" s="9"/>
       <c r="K37" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="20"/>
         <v>1.2000000000000011E-2</v>
       </c>
     </row>
@@ -1516,31 +1516,31 @@
         <v>-1</v>
       </c>
       <c r="C38" s="9">
-        <f>E38*C37/D37</f>
+        <f t="shared" si="18"/>
         <v>58.900316159999988</v>
       </c>
       <c r="D38" s="9">
         <v>2.5</v>
       </c>
       <c r="E38" s="10">
-        <f>2.5+B38</f>
+        <f t="shared" si="19"/>
         <v>1.5</v>
       </c>
       <c r="F38" s="9"/>
       <c r="G38" s="9">
-        <f>C38/D38</f>
+        <f t="shared" si="16"/>
         <v>23.560126463999996</v>
       </c>
       <c r="H38" s="9">
         <v>1.0089999999999999</v>
       </c>
       <c r="I38" s="11">
-        <f>10*H38*(143.254*H38^3-648.67*H38^2+1125.805*H38-620.389)-G38</f>
+        <f t="shared" si="17"/>
         <v>-0.2883901927664887</v>
       </c>
       <c r="J38" s="9"/>
       <c r="K38" s="12">
-        <f t="shared" ref="K38" si="13">H37-H38</f>
+        <f t="shared" ref="K38" si="21">H37-H38</f>
         <v>6.0000000000000053E-3</v>
       </c>
     </row>
@@ -1552,31 +1552,31 @@
         <v>-1.1000000000000001</v>
       </c>
       <c r="C39" s="9">
-        <f>E39*C38/D38</f>
+        <f t="shared" si="18"/>
         <v>32.984177049599992</v>
       </c>
       <c r="D39" s="9">
         <v>2.5</v>
       </c>
       <c r="E39" s="10">
-        <f>2.5+B39</f>
+        <f t="shared" si="19"/>
         <v>1.4</v>
       </c>
       <c r="F39" s="9"/>
       <c r="G39" s="9">
-        <f>C39/D39</f>
+        <f t="shared" si="16"/>
         <v>13.193670819839998</v>
       </c>
       <c r="H39" s="9">
         <v>1.0049999999999999</v>
       </c>
       <c r="I39" s="11">
-        <f>10*H39*(143.254*H39^3-648.67*H39^2+1125.805*H39-620.389)-G39</f>
+        <f t="shared" si="17"/>
         <v>-0.27258474200091598</v>
       </c>
       <c r="J39" s="9"/>
       <c r="K39" s="12">
-        <f t="shared" ref="K39:K40" si="14">H38-H39</f>
+        <f t="shared" ref="K39:K40" si="22">H38-H39</f>
         <v>4.0000000000000036E-3</v>
       </c>
     </row>
@@ -1588,31 +1588,31 @@
         <v>-2.5</v>
       </c>
       <c r="C40" s="14">
-        <f>E40*C39/D39</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="D40" s="14">
         <v>2.5</v>
       </c>
       <c r="E40" s="15">
-        <f>2.5+B40</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="F40" s="14"/>
       <c r="G40" s="14">
-        <f>C40/D40</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="H40" s="14">
         <v>1</v>
       </c>
       <c r="I40" s="16">
-        <f>10*H40*(143.254*H40^3-648.67*H40^2+1125.805*H40-620.389)-G40</f>
+        <f t="shared" si="17"/>
         <v>1.1368683772161603E-12</v>
       </c>
       <c r="J40" s="14"/>
       <c r="K40" s="17">
-        <f t="shared" si="14"/>
+        <f t="shared" si="22"/>
         <v>4.9999999999998934E-3</v>
       </c>
     </row>
@@ -1649,15 +1649,15 @@
       <c r="E44" s="5"/>
       <c r="F44" s="4"/>
       <c r="G44" s="4">
-        <f>C44/D44</f>
+        <f t="shared" ref="G44:G51" si="23">C44/D44</f>
         <v>192</v>
       </c>
       <c r="H44" s="4">
-        <v>1.077</v>
+        <v>1.0740000000000001</v>
       </c>
       <c r="I44" s="6">
-        <f>10*H44*(143.254*H44^3-648.67*H44^2+1125.805*H44-620.389)-G44</f>
-        <v>8.8709861715353497</v>
+        <f t="shared" ref="I44:I51" si="24">10*H44*(143.254*H44^3-648.67*H44^2+1125.805*H44-620.389)-G44</f>
+        <v>0.97747724462453789</v>
       </c>
       <c r="J44" s="4"/>
       <c r="K44" s="7"/>
@@ -1670,32 +1670,32 @@
         <v>-0.6</v>
       </c>
       <c r="C45" s="9">
-        <f>E45*C44/D44</f>
+        <f t="shared" ref="C45:C51" si="25">E45*C44/D44</f>
         <v>364.8</v>
       </c>
       <c r="D45" s="9">
         <v>2.5</v>
       </c>
       <c r="E45" s="10">
-        <f>2.5+B45</f>
+        <f t="shared" ref="E45:E51" si="26">2.5+B45</f>
         <v>1.9</v>
       </c>
       <c r="F45" s="9"/>
       <c r="G45" s="9">
-        <f>C45/D45</f>
+        <f t="shared" si="23"/>
         <v>145.92000000000002</v>
       </c>
       <c r="H45" s="9">
         <v>1.056</v>
       </c>
       <c r="I45" s="11">
-        <f>10*H45*(143.254*H45^3-648.67*H45^2+1125.805*H45-620.389)-G45</f>
+        <f t="shared" si="24"/>
         <v>-0.19860837973783418</v>
       </c>
       <c r="J45" s="9"/>
       <c r="K45" s="12">
         <f>H44-H45</f>
-        <v>2.0999999999999908E-2</v>
+        <v>1.8000000000000016E-2</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
@@ -1706,31 +1706,31 @@
         <v>-0.9</v>
       </c>
       <c r="C46" s="9">
-        <f>E46*C45/D45</f>
+        <f t="shared" si="25"/>
         <v>233.47200000000004</v>
       </c>
       <c r="D46" s="9">
         <v>2.5</v>
       </c>
       <c r="E46" s="10">
-        <f>2.5+B46</f>
+        <f t="shared" si="26"/>
         <v>1.6</v>
       </c>
       <c r="F46" s="9"/>
       <c r="G46" s="9">
-        <f>C46/D46</f>
+        <f t="shared" si="23"/>
         <v>93.388800000000018</v>
       </c>
       <c r="H46" s="9">
         <v>1.036</v>
       </c>
       <c r="I46" s="18">
-        <f>10*H46*(143.254*H46^3-648.67*H46^2+1125.805*H46-620.389)-G46</f>
+        <f t="shared" si="24"/>
         <v>4.9603226865983174E-2</v>
       </c>
       <c r="J46" s="9"/>
       <c r="K46" s="12">
-        <f t="shared" ref="K46:K48" si="15">H45-H46</f>
+        <f t="shared" ref="K46:K48" si="27">H45-H46</f>
         <v>2.0000000000000018E-2</v>
       </c>
     </row>
@@ -1742,31 +1742,31 @@
         <v>-0.9</v>
       </c>
       <c r="C47" s="9">
-        <f>E47*C46/D46</f>
+        <f t="shared" si="25"/>
         <v>149.42208000000002</v>
       </c>
       <c r="D47" s="9">
         <v>2.5</v>
       </c>
       <c r="E47" s="10">
-        <f>2.5+B47</f>
+        <f t="shared" si="26"/>
         <v>1.6</v>
       </c>
       <c r="F47" s="9"/>
       <c r="G47" s="9">
-        <f>C47/D47</f>
+        <f t="shared" si="23"/>
         <v>59.76883200000001</v>
       </c>
       <c r="H47" s="9">
         <v>1.0229999999999999</v>
       </c>
       <c r="I47" s="11">
-        <f>10*H47*(143.254*H47^3-648.67*H47^2+1125.805*H47-620.389)-G47</f>
+        <f t="shared" si="24"/>
         <v>-0.17742842875200182</v>
       </c>
       <c r="J47" s="9"/>
       <c r="K47" s="12">
-        <f t="shared" si="15"/>
+        <f t="shared" si="27"/>
         <v>1.3000000000000123E-2</v>
       </c>
     </row>
@@ -1778,31 +1778,31 @@
         <v>-1</v>
       </c>
       <c r="C48" s="9">
-        <f>E48*C47/D47</f>
+        <f t="shared" si="25"/>
         <v>89.653248000000005</v>
       </c>
       <c r="D48" s="9">
         <v>2.5</v>
       </c>
       <c r="E48" s="10">
-        <f>2.5+B48</f>
+        <f t="shared" si="26"/>
         <v>1.5</v>
       </c>
       <c r="F48" s="9"/>
       <c r="G48" s="9">
-        <f>C48/D48</f>
+        <f t="shared" si="23"/>
         <v>35.861299200000005</v>
       </c>
       <c r="H48" s="9">
         <v>1.014</v>
       </c>
       <c r="I48" s="11">
-        <f>10*H48*(143.254*H48^3-648.67*H48^2+1125.805*H48-620.389)-G48</f>
+        <f t="shared" si="24"/>
         <v>0.36552512669675963</v>
       </c>
       <c r="J48" s="9"/>
       <c r="K48" s="12">
-        <f t="shared" si="15"/>
+        <f t="shared" si="27"/>
         <v>8.999999999999897E-3</v>
       </c>
     </row>
@@ -1814,31 +1814,31 @@
         <v>-0.9</v>
       </c>
       <c r="C49" s="9">
-        <f>E49*C48/D48</f>
+        <f t="shared" si="25"/>
         <v>57.378078720000005</v>
       </c>
       <c r="D49" s="9">
         <v>2.5</v>
       </c>
       <c r="E49" s="10">
-        <f>2.5+B49</f>
+        <f t="shared" si="26"/>
         <v>1.6</v>
       </c>
       <c r="F49" s="9"/>
       <c r="G49" s="9">
-        <f>C49/D49</f>
+        <f t="shared" si="23"/>
         <v>22.951231488000001</v>
       </c>
       <c r="H49" s="9">
         <v>1.0089999999999999</v>
       </c>
       <c r="I49" s="11">
-        <f>10*H49*(143.254*H49^3-648.67*H49^2+1125.805*H49-620.389)-G49</f>
+        <f t="shared" si="24"/>
         <v>0.32050478323350617</v>
       </c>
       <c r="J49" s="9"/>
       <c r="K49" s="12">
-        <f t="shared" ref="K49" si="16">H48-H49</f>
+        <f t="shared" ref="K49" si="28">H48-H49</f>
         <v>5.0000000000001155E-3</v>
       </c>
     </row>
@@ -1850,31 +1850,31 @@
         <v>-1.1000000000000001</v>
       </c>
       <c r="C50" s="9">
-        <f>E50*C49/D49</f>
+        <f t="shared" si="25"/>
         <v>32.131724083199998</v>
       </c>
       <c r="D50" s="9">
         <v>2.5</v>
       </c>
       <c r="E50" s="10">
-        <f>2.5+B50</f>
+        <f t="shared" si="26"/>
         <v>1.4</v>
       </c>
       <c r="F50" s="9"/>
       <c r="G50" s="9">
-        <f>C50/D50</f>
+        <f t="shared" si="23"/>
         <v>12.852689633279999</v>
       </c>
       <c r="H50" s="9">
         <v>1.0049999999999999</v>
       </c>
       <c r="I50" s="11">
-        <f>10*H50*(143.254*H50^3-648.67*H50^2+1125.805*H50-620.389)-G50</f>
+        <f t="shared" si="24"/>
         <v>6.8396444559082781E-2</v>
       </c>
       <c r="J50" s="9"/>
       <c r="K50" s="12">
-        <f t="shared" ref="K50:K51" si="17">H49-H50</f>
+        <f t="shared" ref="K50:K51" si="29">H49-H50</f>
         <v>4.0000000000000036E-3</v>
       </c>
     </row>
@@ -1886,31 +1886,31 @@
         <v>-2.5</v>
       </c>
       <c r="C51" s="14">
-        <f>E51*C50/D50</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="D51" s="14">
         <v>2.5</v>
       </c>
       <c r="E51" s="15">
-        <f>2.5+B51</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="F51" s="14"/>
       <c r="G51" s="14">
-        <f>C51/D51</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="H51" s="14">
         <v>1</v>
       </c>
       <c r="I51" s="16">
-        <f>10*H51*(143.254*H51^3-648.67*H51^2+1125.805*H51-620.389)-G51</f>
+        <f t="shared" si="24"/>
         <v>1.1368683772161603E-12</v>
       </c>
       <c r="J51" s="14"/>
       <c r="K51" s="17">
-        <f t="shared" si="17"/>
+        <f t="shared" si="29"/>
         <v>4.9999999999998934E-3</v>
       </c>
     </row>
